--- a/ig/DM-JUILLET-2026/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -204,7 +204,7 @@
     <t>072</t>
   </si>
   <si>
-    <t>Table de bloc opératoire obésité (poids supérieur à 250 kg) - bariatrique</t>
+    <t>Table de bloc opératoire obésité (poids &gt; 250 kg) - bariatrique</t>
   </si>
   <si>
     <t>083</t>
